--- a/artfynd/A 49528-2022 artfynd.xlsx
+++ b/artfynd/A 49528-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49528-2022 artfynd.xlsx
+++ b/artfynd/A 49528-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96972871</v>
+        <v>96972898</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607893.4239267564</v>
+        <v>607930</v>
       </c>
       <c r="R2" t="n">
-        <v>7096555.733676176</v>
+        <v>7096431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96972907</v>
+        <v>96972888</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608148.8204009959</v>
+        <v>607899</v>
       </c>
       <c r="R3" t="n">
-        <v>7096499.976428937</v>
+        <v>7096454</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2021-07-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,37 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96972888</v>
+        <v>96972871</v>
       </c>
       <c r="B4" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607899.583964843</v>
+        <v>607893</v>
       </c>
       <c r="R4" t="n">
-        <v>7096453.988372371</v>
+        <v>7096556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>2021-07-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96972898</v>
+        <v>96972907</v>
       </c>
       <c r="B5" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607929.8525133203</v>
+        <v>608149</v>
       </c>
       <c r="R5" t="n">
-        <v>7096431.303450259</v>
+        <v>7096500</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1061,9 @@
           <t>2021-07-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 49528-2022 artfynd.xlsx
+++ b/artfynd/A 49528-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96972898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96972888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96972871</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96972907</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>